--- a/data/mapping/diagnosis_kdrg44_mapping_template.xlsx
+++ b/data/mapping/diagnosis_kdrg44_mapping_template.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>630</v>
+        <v>3190</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -466,11 +466,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>무릎관절증</t>
+          <t>담석증</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>311</v>
+        <v>1166</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -478,11 +478,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>담석증</t>
+          <t>무릎관절증</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>290</v>
+        <v>1157</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>269</v>
+        <v>1038</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -502,11 +502,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>뇌경색증</t>
+          <t>호소증상 및 보고된 진단명이 없는 사람의 일반적 검사 및 조사</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>199</v>
+        <v>899</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>862</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>급성 충수염</t>
+          <t>뇌경색증</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>801</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -538,11 +538,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>호소증상 및 보고된 진단명이 없는 사람의 일반적 검사 및 조사</t>
+          <t>급성 충수염</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>790</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>693</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>127</v>
+        <v>516</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>유방의 악성 신생물</t>
+          <t>전정기능의 장애</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119</v>
+        <v>477</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -586,27 +586,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>확인된 계절성 인플루엔자바이러스에 의한 인플루엔자</t>
+          <t>어지럼증 및 어지럼</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>인플루엔자</t>
-        </is>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>급성 세뇨관-간질신장염</t>
+          <t>상세불명 병원체의 폐렴</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108</v>
+        <v>423</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -614,27 +610,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>협심증</t>
+          <t>급성 세뇨관-간질신장염</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>협심증</t>
-        </is>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>어지럼증 및 어지럼</t>
+          <t>편도 및 아데노이드의 만성 질환</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>359</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -642,23 +634,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>상세불명 병원체의 폐렴</t>
+          <t>협심증</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>97</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>357</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>협심증</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>전정기능의 장애</t>
+          <t>아래팔의 골절</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>351</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -666,11 +662,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>장의 기타 질환</t>
+          <t>발목을 포함한 아래다리의 골절</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -678,11 +674,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>요추 및 골반의 골절</t>
+          <t>기타 세균성 장감염</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -690,11 +686,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>폐색성 및 역류성 요로병증</t>
+          <t>심방세동 및 조동</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -702,11 +698,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기타 세균성 장감염</t>
+          <t>두개내손상</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -714,11 +710,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>발목을 포함한 아래다리의 골절</t>
+          <t>신장 및 요관의 결석</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -726,11 +722,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>만성 부비동염</t>
+          <t>장의 기타 질환</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -738,11 +734,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>늑골, 흉골 및 흉추의 골절</t>
+          <t>요추 및 골반의 골절</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -750,11 +746,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>심방세동 및 조동</t>
+          <t>만성 부비동염</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>74</v>
+        <v>309</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -762,11 +758,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>여성생식관의 용종</t>
+          <t>폐색성 및 역류성 요로병증</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>73</v>
+        <v>283</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -774,11 +770,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>신장 및 요관의 결석</t>
+          <t>늑골, 흉골 및 흉추의 골절</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>279</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -790,7 +786,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -798,11 +794,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>어깨 및 위팔의 골절</t>
+          <t>기타 뇌혈관질환</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -810,23 +806,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>편도 및 아데노이드의 만성 질환</t>
+          <t>두통</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>271</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>두통</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>두개내손상</t>
+          <t>비뇨계통의 기타 장애</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -834,11 +834,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>기타 뇌혈관질환</t>
+          <t>어깨 및 위팔의 골절</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -846,11 +846,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>아래팔의 골절</t>
+          <t>장의 게실병</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -858,11 +858,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>비뇨계통의 기타 장애</t>
+          <t>유방의 악성 신생물</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -870,11 +870,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>장의 게실병</t>
+          <t>일과성 뇌허혈발작 및 관련 증후군</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -894,11 +894,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>만성 허혈심장병</t>
+          <t>기타 기능성 장장애</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>55</v>
+        <v>244</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -906,27 +906,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>두통</t>
+          <t>만성 허혈심장병</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>두통</t>
-        </is>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>탈장이 없는 마비성 장폐색증 및 장폐쇄</t>
+          <t>여성생식관의 용종</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -934,23 +930,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>자궁의 평활근종</t>
+          <t>확인된 계절성 인플루엔자바이러스에 의한 인플루엔자</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>인플루엔자</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>어깨병변</t>
+          <t>급성 췌장염</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>51</v>
+        <v>208</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
@@ -958,11 +958,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>일과성 뇌허혈발작 및 관련 증후군</t>
+          <t>알코올성 간질환</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
@@ -982,11 +982,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>기타 기능성 장장애</t>
+          <t>코 및 비동의 기타 장애</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -994,27 +994,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2형 당뇨병</t>
+          <t>자궁의 평활근종</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>43</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>당뇨병</t>
-        </is>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>기타 염증성 간질환</t>
+          <t>어깨병변</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -1022,11 +1018,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>코 및 비동의 기타 장애</t>
+          <t>기타 및 부위불명의 소화계통의 양성 신생물</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
@@ -1034,11 +1030,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>발진티푸스</t>
+          <t>기타 염증성 간질환</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -1046,11 +1042,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>사타구니탈장</t>
+          <t>탈장이 없는 마비성 장폐색증 및 장폐쇄</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
@@ -1058,11 +1054,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>기타 및 부위불명의 소화계통의 양성 신생물</t>
+          <t>사타구니탈장</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -1070,11 +1066,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>급성 췌장염</t>
+          <t>대상포진</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
@@ -1082,23 +1078,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>췌장의 악성 신생물</t>
+          <t>2형 당뇨병</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>39</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>당뇨병</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>알코올성 간질환</t>
+          <t>두개골 및 안면골의 골절</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
@@ -1106,13 +1106,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>위의 악성 신생물</t>
+          <t>실신 및 허탈</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>36</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>실신 및 허탈</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1122,7 +1126,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
@@ -1130,11 +1134,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>급성 심근경색증</t>
+          <t>무릎의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -1142,11 +1146,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>수분, 전해질 및 산-염기균형의 기타 장애</t>
+          <t>급성 심근경색증</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
@@ -1154,11 +1158,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>대상포진</t>
+          <t>기타 패혈증</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -1166,11 +1170,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>기타 패혈증</t>
+          <t>연조직염</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
@@ -1178,11 +1182,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>무릎의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+          <t>자궁내막증</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -1190,11 +1194,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>뇌내출혈</t>
+          <t>결장의 악성 신생물</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
@@ -1202,27 +1206,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>급성 신부전</t>
+          <t>양성 지방종성 신생물</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>급성 신부전</t>
-        </is>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>결장의 악성 신생물</t>
+          <t>발작성 빈맥</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
@@ -1230,11 +1230,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>기타 척추병증</t>
+          <t>뇌내출혈</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -1242,11 +1242,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>두개골 및 안면골의 골절</t>
+          <t>기타 청력소실</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
@@ -1254,11 +1254,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>장의 혈관장애</t>
+          <t>무릎의 내부장애</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -1266,11 +1266,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>자궁내막증</t>
+          <t>수분, 전해질 및 산-염기균형의 기타 장애</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
@@ -1278,11 +1278,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>위궤양</t>
+          <t>치핵 및 항문주위정맥혈전증</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -1290,11 +1290,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>유방의 양성 신생물</t>
+          <t>달리 분류되지 않은 처치의 합병증</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
@@ -1302,11 +1302,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>연조직염</t>
+          <t>위의 악성 신생물</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -1314,11 +1314,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>발목을 제외한 발의 골절</t>
+          <t>위궤양</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
@@ -1326,11 +1326,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>전립선의 악성 신생물</t>
+          <t>편도주위농양</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -1338,55 +1338,51 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>실신 및 허탈</t>
+          <t>기타 척추병증</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>실신 및 허탈</t>
-        </is>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>팔의 단일신경병증</t>
+          <t>심부전</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
-      </c>
-      <c r="C75" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>체내용 심박기 설치술(급성심근경색, 심부전, 쇼크의 경우)</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>심부전</t>
+          <t>바이러스성 및 기타 명시된 장감염</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>25</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>체내용 심박기 설치술(급성심근경색, 심부전, 쇼크의 경우)</t>
-        </is>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>치핵 및 항문주위정맥혈전증</t>
+          <t>유방의 양성 신생물</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -1394,11 +1390,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>편도주위농양</t>
+          <t>발목을 제외한 발의 골절</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
@@ -1406,11 +1402,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>소화계통의 기타 질환</t>
+          <t>췌장의 악성 신생물</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
@@ -1418,11 +1414,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>수행되지 않은 특정 처치를 위해 보건서비스에 접하고 있는 사람</t>
+          <t>내부 정형외과적 인공삽입장치, 삽입물 및 이식편의 합병증</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -1430,23 +1426,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>전립선의 염증성 질환</t>
+          <t>담낭염</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>24</v>
-      </c>
-      <c r="C81" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>담낭염 또는 담관염을 동반한 담도질환</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>담도의 기타 및 상세불명 부분의 악성 신생물</t>
+          <t>전립선의 염증성 질환</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -1454,11 +1454,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 처치의 합병증</t>
+          <t>수행되지 않은 특정 처치를 위해 보건서비스에 접하고 있는 사람</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
@@ -1466,11 +1466,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>발작성 빈맥</t>
+          <t>전립선의 악성 신생물</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -1478,11 +1478,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>내부 정형외과적 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+          <t>손목 및 손부위의 골절</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
@@ -1490,23 +1490,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>복부 및 골반 통증</t>
+          <t>기타 및 원인미상의 열</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>23</v>
-      </c>
-      <c r="C86" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>열</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>무릎의 내부장애</t>
+          <t>요추 및 골반의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
@@ -1514,23 +1518,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>손목 및 손부위의 골절</t>
+          <t>급성 신부전</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22</v>
-      </c>
-      <c r="C88" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>급성 신부전</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>위 및 십이지장의 기타 질환</t>
+          <t>급성 편도염</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
@@ -1538,11 +1546,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>양성 지방종성 신생물</t>
+          <t>소화계통의 기타 질환</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -1554,7 +1562,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
@@ -1562,11 +1570,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>기타 청력소실</t>
+          <t>담낭의 기타 질환</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -1574,11 +1582,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>기타 급성 바이러스간염</t>
+          <t>U07의 응급사용</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
@@ -1586,11 +1594,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>난소의 양성 신생물</t>
+          <t>위 및 십이지장의 기타 질환</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -1598,11 +1606,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>방광의 악성 신생물</t>
+          <t>기타 급성 바이러스간염</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
@@ -1610,27 +1618,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>기타 및 원인미상의 열</t>
+          <t>의심되는 질병 및 병태를 위한 의학적 관찰 및 평가, 배제된</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>19</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>열</t>
-        </is>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>요추 및 골반의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+          <t>팔의 단일신경병증</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
@@ -1638,27 +1642,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>담낭염</t>
+          <t>뇌경색증을 유발하지 않은 뇌전동맥의 폐쇄 및 협착</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>18</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>담낭염 또는 담관염을 동반한 담도질환</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 바이러스폐렴</t>
+          <t>손가락 및 발가락의 후천변형</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
@@ -1666,11 +1666,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>유방의 제자리암종</t>
+          <t>악성 신생물 이외의 병태에 대한 치료후 추적검사</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -1678,11 +1678,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>간의 섬유증 및 경변증</t>
+          <t>복부 및 골반 통증</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
